--- a/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/eb85b1299b9076c2/ドキュメント/Unity/Okashi_Atlier2/Assets/Resources/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55441E28-7E1B-465D-8955-06FA3BF68ADE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="22" documentId="13_ncr:1_{55441E28-7E1B-465D-8955-06FA3BF68ADE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B314769-B2C4-4D4A-997E-E1F86AC4F406}"/>
   <bookViews>
-    <workbookView xWindow="1995" yWindow="1185" windowWidth="25005" windowHeight="14355" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="3270" yWindow="1650" windowWidth="23295" windowHeight="13305" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -3381,28 +3381,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>次に作るお菓子の成功率を一時的に上げる。</t>
-    <rPh sb="0" eb="1">
-      <t>ツギ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="8" eb="11">
-      <t>セイコウリツ</t>
-    </rPh>
-    <rPh sb="12" eb="15">
-      <t>イチジテキ</t>
-    </rPh>
-    <rPh sb="16" eb="17">
-      <t>ア</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>クレッセント・ムーン</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -3837,52 +3815,6 @@
     </rPh>
     <rPh sb="94" eb="96">
       <t>ショウヒ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>次に作るお菓子の成功率を一時的に上げる「エピクレイシス状態」になる。
-しばらくの間、エピクレイシス状態は続く。
-また、一回お菓子・仕上げ・魔法を使用すると消える。
-LVを上げると、確率を上昇させることができる。
-LV1: +30%
-LV2: +40%
-LV3: +50%</t>
-    <rPh sb="27" eb="29">
-      <t>ジョウタイ</t>
-    </rPh>
-    <rPh sb="41" eb="42">
-      <t>アイダ</t>
-    </rPh>
-    <rPh sb="50" eb="52">
-      <t>ジョウタイ</t>
-    </rPh>
-    <rPh sb="53" eb="54">
-      <t>ツヅ</t>
-    </rPh>
-    <rPh sb="60" eb="62">
-      <t>イッカイ</t>
-    </rPh>
-    <rPh sb="63" eb="65">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="66" eb="68">
-      <t>シア</t>
-    </rPh>
-    <rPh sb="70" eb="72">
-      <t>マホウ</t>
-    </rPh>
-    <rPh sb="73" eb="75">
-      <t>シヨウ</t>
-    </rPh>
-    <rPh sb="78" eb="79">
-      <t>キ</t>
-    </rPh>
-    <rPh sb="92" eb="94">
-      <t>カクリツ</t>
-    </rPh>
-    <rPh sb="95" eb="97">
-      <t>ジョウショウ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -4667,6 +4599,56 @@
 LVが上がると、効果もアップする。</t>
     <rPh sb="21" eb="22">
       <t>ハ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>一定時間お菓子の成功率を一時的に上げる。</t>
+    <rPh sb="0" eb="4">
+      <t>イッテイジカン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="8" eb="11">
+      <t>セイコウリツ</t>
+    </rPh>
+    <rPh sb="12" eb="15">
+      <t>イチジテキ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>一定時間お菓子の成功率を一時的に上げる「エピクレイシス状態」になる。
+しばらくの間、エピクレイシス状態は続く。
+LVを上げると、確率を上昇させることができる。
+LV1ごとに2時間のびる。
+LV1: +35%
+LV2: +65%
+LV3: +95%</t>
+    <rPh sb="0" eb="4">
+      <t>イッテイジカン</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="41" eb="42">
+      <t>アイダ</t>
+    </rPh>
+    <rPh sb="50" eb="52">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="53" eb="54">
+      <t>ツヅ</t>
+    </rPh>
+    <rPh sb="66" eb="68">
+      <t>カクリツ</t>
+    </rPh>
+    <rPh sb="69" eb="71">
+      <t>ジョウショウ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -4788,6 +4770,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5143,13 +5129,13 @@
         <v>51</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>228</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="P1" s="1" t="s">
         <v>8</v>
@@ -5167,7 +5153,7 @@
         <v>91</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="V1" s="1" t="s">
         <v>52</v>
@@ -5320,7 +5306,7 @@
         <v>0</v>
       </c>
       <c r="V3" s="7" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="W3" t="s">
         <v>93</v>
@@ -5545,7 +5531,7 @@
         <v>0</v>
       </c>
       <c r="V6" s="7" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="W6" t="s">
         <v>53</v>
@@ -5563,16 +5549,16 @@
         <v>1012</v>
       </c>
       <c r="C7" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D7" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E7" t="s">
+        <v>334</v>
+      </c>
+      <c r="F7" t="s">
         <v>335</v>
-      </c>
-      <c r="F7" t="s">
-        <v>336</v>
       </c>
       <c r="G7">
         <v>6</v>
@@ -5620,7 +5606,7 @@
         <v>0</v>
       </c>
       <c r="V7" s="7" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="W7" t="s">
         <v>53</v>
@@ -5938,16 +5924,16 @@
         <v>1011</v>
       </c>
       <c r="C12" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D12" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E12" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="F12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="G12">
         <v>6</v>
@@ -5995,7 +5981,7 @@
         <v>0</v>
       </c>
       <c r="V12" s="7" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="W12" t="s">
         <v>160</v>
@@ -6295,7 +6281,7 @@
         <v>0</v>
       </c>
       <c r="V16" s="7" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="W16" t="s">
         <v>93</v>
@@ -6370,7 +6356,7 @@
         <v>0</v>
       </c>
       <c r="V17" s="7" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="W17" t="s">
         <v>93</v>
@@ -6544,7 +6530,7 @@
         <v>244</v>
       </c>
       <c r="E20" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="F20" t="s">
         <v>245</v>
@@ -6763,7 +6749,7 @@
         <v>3006</v>
       </c>
       <c r="C23" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D23" t="s">
         <v>154</v>
@@ -6772,7 +6758,7 @@
         <v>153</v>
       </c>
       <c r="F23" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="G23">
         <v>2</v>
@@ -6820,7 +6806,7 @@
         <v>0</v>
       </c>
       <c r="V23" s="7" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="W23" t="s">
         <v>93</v>
@@ -6895,7 +6881,7 @@
         <v>0</v>
       </c>
       <c r="V24" s="7" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="W24" t="s">
         <v>93</v>
@@ -7045,7 +7031,7 @@
         <v>0</v>
       </c>
       <c r="V26" s="7" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="W26" t="s">
         <v>20</v>
@@ -7120,7 +7106,7 @@
         <v>0</v>
       </c>
       <c r="V27" s="7" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="W27" t="s">
         <v>93</v>
@@ -7138,7 +7124,7 @@
         <v>3009</v>
       </c>
       <c r="C28" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D28" t="s">
         <v>316</v>
@@ -7168,7 +7154,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="N28" t="s">
         <v>93</v>
@@ -7189,13 +7175,13 @@
         <v>100</v>
       </c>
       <c r="T28">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="U28">
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="V28" s="7" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="W28" t="s">
         <v>93</v>
@@ -7213,16 +7199,16 @@
         <v>3010</v>
       </c>
       <c r="C29" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D29" t="s">
+        <v>332</v>
+      </c>
+      <c r="E29" t="s">
+        <v>357</v>
+      </c>
+      <c r="F29" t="s">
         <v>333</v>
-      </c>
-      <c r="E29" t="s">
-        <v>358</v>
-      </c>
-      <c r="F29" t="s">
-        <v>334</v>
       </c>
       <c r="G29">
         <v>4</v>
@@ -7270,7 +7256,7 @@
         <v>0</v>
       </c>
       <c r="V29" s="7" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="W29" t="s">
         <v>93</v>
@@ -7720,7 +7706,7 @@
         <v>0</v>
       </c>
       <c r="V35" s="7" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="W35" t="s">
         <v>93</v>
@@ -7870,7 +7856,7 @@
         <v>0</v>
       </c>
       <c r="V37" s="7" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="W37" t="s">
         <v>23</v>
@@ -8263,7 +8249,7 @@
         <v>4003</v>
       </c>
       <c r="C43" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="D43" t="s">
         <v>25</v>
@@ -8272,7 +8258,7 @@
         <v>70</v>
       </c>
       <c r="F43" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="G43">
         <v>3</v>
@@ -8320,7 +8306,7 @@
         <v>0</v>
       </c>
       <c r="V43" s="7" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="W43" t="s">
         <v>93</v>
@@ -8395,7 +8381,7 @@
         <v>0</v>
       </c>
       <c r="V44" s="7" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="W44" t="s">
         <v>151</v>
@@ -9088,16 +9074,16 @@
         <v>5007</v>
       </c>
       <c r="C54" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D54" t="s">
+        <v>344</v>
+      </c>
+      <c r="E54" t="s">
+        <v>343</v>
+      </c>
+      <c r="F54" t="s">
         <v>345</v>
-      </c>
-      <c r="E54" t="s">
-        <v>344</v>
-      </c>
-      <c r="F54" t="s">
-        <v>346</v>
       </c>
       <c r="G54">
         <v>6</v>
@@ -9145,7 +9131,7 @@
         <v>0</v>
       </c>
       <c r="V54" s="7" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="W54" t="s">
         <v>93</v>
@@ -9220,7 +9206,7 @@
         <v>0</v>
       </c>
       <c r="V55" s="7" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="W55" t="s">
         <v>260</v>
@@ -9298,7 +9284,7 @@
         <v>227</v>
       </c>
       <c r="W56" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="X56">
         <v>2</v>
@@ -9538,16 +9524,16 @@
         <v>5006</v>
       </c>
       <c r="C60" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D60" t="s">
+        <v>341</v>
+      </c>
+      <c r="E60" t="s">
+        <v>340</v>
+      </c>
+      <c r="F60" t="s">
         <v>342</v>
-      </c>
-      <c r="E60" t="s">
-        <v>341</v>
-      </c>
-      <c r="F60" t="s">
-        <v>343</v>
       </c>
       <c r="G60">
         <v>6</v>
@@ -9574,7 +9560,7 @@
         <v>229</v>
       </c>
       <c r="O60" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="P60">
         <v>1</v>
@@ -9595,7 +9581,7 @@
         <v>0</v>
       </c>
       <c r="V60" s="7" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="W60" t="s">
         <v>93</v>
@@ -9613,16 +9599,16 @@
         <v>5007</v>
       </c>
       <c r="C61" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D61" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E61" t="s">
+        <v>320</v>
+      </c>
+      <c r="F61" t="s">
         <v>321</v>
-      </c>
-      <c r="F61" t="s">
-        <v>322</v>
       </c>
       <c r="G61">
         <v>6</v>
@@ -9670,7 +9656,7 @@
         <v>0</v>
       </c>
       <c r="V61" s="7" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="W61" t="s">
         <v>38</v>
@@ -9688,22 +9674,22 @@
         <v>5007</v>
       </c>
       <c r="C62" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D62" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E62" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F62" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="G62">
         <v>6</v>
       </c>
       <c r="H62">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="I62">
         <v>0</v>
@@ -9718,7 +9704,7 @@
         <v>0</v>
       </c>
       <c r="M62" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="N62" t="s">
         <v>93</v>
@@ -9739,13 +9725,13 @@
         <v>100</v>
       </c>
       <c r="T62">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="U62">
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="V62" s="7" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="W62" t="s">
         <v>93</v>
@@ -9913,16 +9899,16 @@
         <v>6008</v>
       </c>
       <c r="C65" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="D65" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E65" t="s">
+        <v>337</v>
+      </c>
+      <c r="F65" t="s">
         <v>338</v>
-      </c>
-      <c r="F65" t="s">
-        <v>339</v>
       </c>
       <c r="G65">
         <v>6</v>
@@ -9949,7 +9935,7 @@
         <v>229</v>
       </c>
       <c r="O65" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="P65">
         <v>1</v>
@@ -9970,7 +9956,7 @@
         <v>0</v>
       </c>
       <c r="V65" s="7" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="W65" t="s">
         <v>93</v>
@@ -10045,7 +10031,7 @@
         <v>0</v>
       </c>
       <c r="V66" s="7" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="W66" t="s">
         <v>93</v>
@@ -10120,7 +10106,7 @@
         <v>0</v>
       </c>
       <c r="V67" s="7" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="W67" t="s">
         <v>93</v>
@@ -10138,7 +10124,7 @@
         <v>6006</v>
       </c>
       <c r="C68" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D68" t="s">
         <v>319</v>
@@ -10147,13 +10133,13 @@
         <v>318</v>
       </c>
       <c r="F68" t="s">
-        <v>320</v>
+        <v>394</v>
       </c>
       <c r="G68">
         <v>6</v>
       </c>
       <c r="H68">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="I68">
         <v>0</v>
@@ -10168,7 +10154,7 @@
         <v>0</v>
       </c>
       <c r="M68" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="N68" t="s">
         <v>93</v>
@@ -10189,19 +10175,19 @@
         <v>100</v>
       </c>
       <c r="T68">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="U68">
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="V68" s="7" t="s">
-        <v>364</v>
+        <v>395</v>
       </c>
       <c r="W68" t="s">
         <v>99</v>
       </c>
       <c r="X68">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69" spans="1:24" s="3" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -10216,13 +10202,13 @@
         <v>265</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E69" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="F69" s="3" t="s">
         <v>329</v>
-      </c>
-      <c r="F69" s="3" t="s">
-        <v>330</v>
       </c>
       <c r="G69" s="3">
         <v>6</v>
@@ -10270,7 +10256,7 @@
         <v>0</v>
       </c>
       <c r="V69" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="W69" s="3" t="s">
         <v>93</v>
@@ -10663,7 +10649,7 @@
         <v>9001</v>
       </c>
       <c r="C75" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="D75" t="s">
         <v>77</v>
@@ -10720,7 +10706,7 @@
         <v>0</v>
       </c>
       <c r="V75" s="7" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="W75" t="s">
         <v>93</v>
